--- a/data/content.xlsx
+++ b/data/content.xlsx
@@ -18580,6 +18580,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -18635,7 +18636,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>assets/images/history/1857/flag.png</t>
+          <t>assets/2-history-of-tiranga/1857/flag/flag.png</t>
         </is>
       </c>
     </row>
@@ -18662,7 +18663,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>assets/images/history/1905/flag.png</t>
+          <t>assets/2-history-of-tiranga/1905/flag/flag.png</t>
         </is>
       </c>
     </row>
@@ -18824,7 +18825,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>assets/images/history/1941/flag.png</t>
+          <t>assets/2-history-of-tiranga/1941/flag/flag.png</t>
         </is>
       </c>
     </row>
@@ -18893,7 +18894,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>

--- a/data/content.xlsx
+++ b/data/content.xlsx
@@ -746,6 +746,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -1026,7 +1027,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Era backgrounds bg-1 for 1906-1947 + timeline thumbnails: client design handoff (Freepik Mystic 4K scene renders; historical flags composited via Nano Banana Pro). Representative scene art, not archival photographs.</t>
+          <t>Era backgrounds bg-1: 1906-1947 from client design handoff (Freepik Mystic 4K scene renders; flags composited via Nano Banana Pro); 1857, 1905 and 1941 generated to match via Magnific (Nano Banana, sepia era scenes). Representative scene art, not archival photographs.</t>
         </is>
       </c>
     </row>
@@ -18580,7 +18581,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>

--- a/data/content.xlsx
+++ b/data/content.xlsx
@@ -746,7 +746,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -6489,6 +6488,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -6931,6 +6931,11 @@
           <t>Sentinel Assam (8 Jan 2025)</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://flagfoundationofindia.in/uploads/image-galleries/01KJ4DDWQ5K951609Z3XBQHVNV.jpeg</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -7037,6 +7042,11 @@
           <t>https://flagfoundationofindia.in/monumental-flags</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://flagfoundationofindia.in/uploads/image-galleries/01KJ4D9BFMX8XH3ZJFZYK3ZH42.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -7307,6 +7317,11 @@
           <t>https://flagfoundationofindia.in/monumental-flags</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://flagfoundationofindia.in/uploads/image-galleries/01KNM2F8EQY0NNHBDDCB6M0QTT.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -7630,6 +7645,11 @@
           <t>https://flagfoundationofindia.in/</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://flagfoundationofindia.in/uploads/image-galleries/01KJ4ESPXPDJ7GSFK1BAR0QMTW.png</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -7905,6 +7925,11 @@
           <t>https://flagfoundationofindia.in/monumental-flags</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://flagfoundationofindia.in/uploads/image-galleries/01KHNQPT53BAPWVMVWKGHB40RC.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -8513,6 +8538,11 @@
           <t>https://flagfoundationofindia.in/monumental-flags</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>https://flagfoundationofindia.in/uploads/image-galleries/01KHRBTN693MTBGW9R2W5PXT7P.jpeg</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -9237,6 +9267,11 @@
           <t>https://flagfoundationofindia.in/monumental-flags</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>https://flagfoundationofindia.in/uploads/image-galleries/01KHN305J9F8WZDDVFTE25SC34.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -9971,6 +10006,11 @@
           <t>https://flagfoundationofindia.in/monumental-flags</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>https://flagfoundationofindia.in/uploads/image-galleries/01KHN97RT6PQXTV0EQBXX2B36R.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -10193,6 +10233,11 @@
           <t>https://flagfoundationofindia.in/monumental-flags</t>
         </is>
       </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>https://flagfoundationofindia.in/uploads/image-galleries/01KHN4NYXTP7BX9ERRN8PFS8DV.webp</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -10791,6 +10836,11 @@
           <t>https://flagfoundationofindia.in/monumental-flags</t>
         </is>
       </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>https://flagfoundationofindia.in/uploads/image-galleries/01KHN9D9MK5Z01RJ22637D1FKB.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -11785,6 +11835,11 @@
           <t>https://flagfoundationofindia.in/monumental-flags</t>
         </is>
       </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>https://flagfoundationofindia.in/uploads/image-galleries/01KHNAMC6KZ9TWH2N78TV6GD3F.png</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -12499,6 +12554,11 @@
           <t>https://flagfoundationofindia.in/monumental-flags</t>
         </is>
       </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>https://flagfoundationofindia.in/uploads/image-galleries/01KNM23E4HSBFQGT5Y6GN48PFR.png</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12759,6 +12819,11 @@
           <t>https://flagfoundationofindia.in/monumental-flags</t>
         </is>
       </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>https://flagfoundationofindia.in/uploads/image-galleries/01KHN5GK75DZD1F1X5B0X12H3A.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12860,6 +12925,11 @@
           <t>https://flagfoundationofindia.in/monumental-flags</t>
         </is>
       </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>https://flagfoundationofindia.in/uploads/image-galleries/01KNM330FWE2FYVDQE504W4990.jpeg</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13135,6 +13205,11 @@
           <t>https://flagfoundationofindia.in/monumental-flags</t>
         </is>
       </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>https://flagfoundationofindia.in/uploads/image-galleries/01KHQWH97PSNXJCKVNA8NNBM3S.webp</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13791,6 +13866,11 @@
           <t>https://theprint.in/india/flag-foundation-of-india-president-naveen-jindal-unfurls-108-ft-tall-tricolor-in-pune/1549558/</t>
         </is>
       </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>https://flagfoundationofindia.in/uploads/image-galleries/01KHR7H7RB7HRAPCFZ97XRMN5P.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15118,6 +15198,11 @@
           <t>https://flagfoundationofindia.in/monumental-flags</t>
         </is>
       </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>https://flagfoundationofindia.in/uploads/image-galleries/01KHN9M0B5FA7W4RWDZX5XS4PC.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -15224,6 +15309,11 @@
           <t>https://flagfoundationofindia.in/</t>
         </is>
       </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>https://flagfoundationofindia.in/uploads/image-galleries/01KHT5KV8S66CDG4RNRBP19G6Z.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -15335,6 +15425,11 @@
           <t>https://flagfoundationofindia.in/monumental-flags</t>
         </is>
       </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>https://flagfoundationofindia.in/uploads/image-galleries/01KHN9B7PVKA4WB9B1BY527ZB0.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -15658,6 +15753,11 @@
           <t>https://flagfoundationofindia.in/monumental-flags</t>
         </is>
       </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>https://flagfoundationofindia.in/uploads/image-galleries/01KHR6S2C0PGWNHQGVEXCHQNQ9.png</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -16281,6 +16381,11 @@
           <t>https://flagfoundationofindia.in/monumental-flags</t>
         </is>
       </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>https://flagfoundationofindia.in/uploads/image-galleries/01KHT3FS17JQ8MSYDXSA5J9XAV.jpeg</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -16329,6 +16434,11 @@
           <t>https://flagfoundationofindia.in/monumental-flags</t>
         </is>
       </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>https://flagfoundationofindia.in/uploads/image-galleries/01KJ4G81YBYDHFAWFKY17Z4Q8B.png</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -16929,6 +17039,11 @@
           <t>https://flagfoundationofindia.in/monumental-flags</t>
         </is>
       </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>https://flagfoundationofindia.in/uploads/image-galleries/01KHT41EE6VM48JGR7VZMNRXA9.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -17252,6 +17367,11 @@
           <t>https://flagfoundationofindia.in/monumental-flags</t>
         </is>
       </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>https://flagfoundationofindia.in/uploads/image-galleries/01KHT7TZXGJPWSBBA8PQ3PX10H.jpeg</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -17633,6 +17753,11 @@
           <t>https://flagfoundationofindia.in/monumental-flags</t>
         </is>
       </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>https://flagfoundationofindia.in/uploads/image-galleries/01KHN5D24957KQM0JXB82YNA6Z.webp</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -18335,6 +18460,11 @@
       <c r="K219" t="inlineStr">
         <is>
           <t>https://flagfoundationofindia.in/monumental-flags</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>https://flagfoundationofindia.in/uploads/image-galleries/01KHQXXW1100AHT9YHPYT2K5CD.jpg</t>
         </is>
       </c>
     </row>

--- a/data/content.xlsx
+++ b/data/content.xlsx
@@ -15,6 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 · Sources" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 · Flag Facts (Official)" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09 · Flag Design &amp; Sizes" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 · Image Credits" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -23,13 +24,20 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="12"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -52,8 +60,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4038,6 +4048,2570 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G74"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Image Credits &amp; Provenance Register — every visual asset in the kiosk</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Wikimedia entries re-verified against the Commons API on 2026-07-20. Proof column: click to see the public license/file page. Asset paths are under assets/.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Depicts / Title</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Rights / License</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Proof</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>History gallery</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1857/gallery/gallery-1.png</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bahadur Shah II of India</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Bahadur Shah II of India.jpg (author: Unknown author; date: circa 1850)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Public domain</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Bahadur_Shah_II_of_India.jpg</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-07-20; Aspect diff 0.013% vs installed 1138x1400. Cropped from File:Bahadur Shah II (r. 1837-58), last Mughal emperor of India.jpg.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>History gallery</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1857/gallery/gallery-2.png</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>The Emperor Bahadur Shah II Enthroned</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:The Emperor Bahadur Shah II Enthroned.jpg (author: Ghulam 'Ali Khan (active c. 1820-c. 1840); date: dated 1838 (A.H. 1254))</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Public domain</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:The_Emperor_Bahadur_Shah_II_Enthroned.jpg</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-07-20; Installed 900x769 is exactly the Commons original size.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>History gallery</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1857/gallery/gallery-3.png</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>The Sepoy revolt at Meerut</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:The Sepoy revolt at Meerut.jpg (author: The Illustrated Times; date: 1857-07-11)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Public domain</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:The_Sepoy_revolt_at_Meerut.jpg</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-07-20; Installed 806x600 is exactly the Commons original size.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>History gallery</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1857/gallery/gallery-4.png</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Capture of Delhi, 1857.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Capture of Delhi, 1857..jpg (author: Coloured lithograph by Bequet Freres after R de Moraine, published by E Morier, Paris, 1858 (c).; date: 1858)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Public domain</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Capture_of_Delhi,_1857..jpg</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-07-20; Installed 862x609 is exactly the Commons original size. Source: National Army Museum collection (acc 1971-02-33-139-1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>History gallery</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1905/gallery/gallery-1.png</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ভগিনী নিবেদিতা</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:ভগিনী নিবেদিতা.jpg (author: Unknown author; date: before 1912)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Public domain</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:%E0%A6%AD%E0%A6%97%E0%A6%BF%E0%A6%A8%E0%A7%80_%E0%A6%A8%E0%A6%BF%E0%A6%AC%E0%A7%87%E0%A6%A6%E0%A6%BF%E0%A6%A4%E0%A6%BE.jpg</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-07-20; Found via Category:Sister Nivedita — the only Commons file with the exact 664x940 original dimensions. Title is Bengali for 'Bhagini Nibedita' (Sister Nivedita); file description reads 'Sister Nivedita'. Credit line on the page points to hinduhistory.info article 'Sister Nivedita: India's Irish Daughter'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>History gallery</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1905/gallery/gallery-2.png</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Josephine MacLeod, Mrs. Ole Bull (sitting), Swami Vivekananda and Sister Nivedita in Kashmir, 1898</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Josephine MacLeod, Mrs. Ole Bull (sitting), Swami Vivekananda and Sister Nivedita in Kashmir, 1898.jpg (author: Unknown author; date: 1898-09-20)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Public domain</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Josephine_MacLeod,_Mrs._Ole_Bull_(sitting),_Swami_Vivekananda_and_Sister_Nivedita_in_Kashmir,_1898.jpg</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-07-20; Original dimensions 1200x884 match the installed file exactly. Source credited to Google Arts &amp; Culture asset 'Swami Vivekananda with his western devotees at Kashmir'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>History gallery</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1905/gallery/gallery-3.png</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Indian National Congress 1904</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Indian National Congress 1904.jpg (author: Unknown author; date: 1911 (per file page; publication date of source book 'Indian and home memories' by Sir Henry John Cotton — photo depicts the Dec 1904 Bombay session))</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Public domain</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Indian_National_Congress_1904.jpg</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-07-20; Installed 1400x1108 is a downscale of the 2920x2312 original; aspect ratios differ by ~0.05%, well within 1%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>History gallery</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1905/gallery/gallery-4.png</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Sarada Devi and Sister Nivedita</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Sarada Devi and Sister Nivedita.jpg (author: Anonymous; date: circa 1900)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Public domain</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Sarada_Devi_and_Sister_Nivedita.jpg</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-07-20; Original dimensions 480x591 match the installed file exactly. Transferred to Commons from en.wikipedia; original source contemplative-vedanta.org.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>History gallery</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1906/gallery/gallery-1.png</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Sachindra Prasad Bose</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Sachindra Prasad Bose.jpg (author: Calcutta state archives; date: before 1960)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Public domain</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Sachindra_Prasad_Bose.jpg</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-07-20; Installed 960x1329 vs original 1681x2328; aspect diff 0.04%. Credit: Calcutta state archives.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>History gallery</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1906/gallery/gallery-2.png</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Bande mataram</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Bande mataram.jpg (author: Unknown author; date: 1906-09-29)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Public domain</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Bande_mataram.jpg</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-07-20; Provisional label said front page of 29 Sep 1907, but the Commons file page dates it 1906-09-29 — exhibit caption should say 1906. Aspect diff 0.02%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>History gallery</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1906/gallery/gallery-3.png</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Bipin Chandra Pal</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Bipin Chandra Pal.jpg (author: Unknown; date: ca. 1910s)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Public domain</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Bipin_Chandra_Pal.jpg</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-07-20; Exact pixel match to installed file (797x1000). Credit: Calcutta state archives.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>History gallery</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1906/gallery/gallery-4.png</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Surendranath Bannerjee</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Surendranath Bannerjee.jpg (author: Unknown author; date: 1925)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Public domain</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Surendranath_Bannerjee.jpg</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-07-20; Exact pixel match to installed file (681x1042). Credit: The Modern Review, September 1925.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>History gallery</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1907/gallery/gallery-1.png</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Pencil sketch: Madam Bhikhaji Cama with her flag</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>FFOI book 'Know Your National Flag' (Lt Cdr KV Singh, Flag Foundation of India, 2013), p. 38 (scan)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>(c) Flag Foundation of India — client's own publication</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Book p. 38</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>History gallery</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1907/gallery/gallery-2.png</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Madam Bhikaiji Cama</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Madam Bhikaiji Cama.jpg (author: Unknown author; date: before 13 August 1936 (per file page; portrait of Bhikaiji Cama, d. 1936))</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Public domain</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Madam_Bhikaiji_Cama.jpg</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-07-20; Original aspect 0.60350 vs installed 845x1400 = 0.60357; deviation 0.012%. Extmetadata Artist field renders as 'Unknown author' (duplicated by template).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>History gallery</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1907/gallery/gallery-3.png</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Madam Cama and S. R. Rana</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Madam Cama and S. R. Rana.jpg (author: Unknown author; date: 1907)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Public domain</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Madam_Cama_and_S._R._Rana.jpg</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-07-20; Installed 644x988 is pixel-identical to the Commons original (deviation 0.000%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>History gallery</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1907/gallery/gallery-4.png</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Das Internationale Bureau der II. Internationale vor der Stuttgarter Liederhalle</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Das Internationale Bureau der II. Internationale vor der Stuttgarter Liederhalle.jpg (author: AdsD / Friedrich-Ebert-Stiftung; date: 1907)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Public domain</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Das_Internationale_Bureau_der_II._Internationale_vor_der_Stuttgarter_Liederhalle.jpg</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-07-20; Exact title found via Commons namespace-6 search. Group photo of the International Bureau of the Second International in front of the Stuttgart Liederhalle (1907 International Socialist Congress); Rosa Luxemburg marked with a white cross. Aspect 1.46358 vs installed 1400x957 = 1.46290; deviation 0.046%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>History gallery</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1917/gallery/gallery-1.png</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Portrait of Annie Besant (1847 – 1933), c. 1910</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Portrait of Annie Besant (1847 – 1933), c. 1910.jpg (author: Falk Studio, Sydney; date: circa 1910 (vintage gelatin silver print, State Library of New South Wales, PXA 1023))</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Public domain</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Portrait_of_Annie_Besant_(1847_%E2%80%93_1933),_c._1910.jpg</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-07-20; Provisional title checked out except the dash: the exact Commons title uses an en dash (1847 – 1933), not a hyphen. Aspect 677/960 = 0.70521 vs installed 500/709 = 0.70522 (diff ~0.002%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>History gallery</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1917/gallery/gallery-2.png</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Young India; an interpretation and a history of the nationalist movement from within (1916) (14781987942)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Young India; an interpretation and a history of the nationalist movement from within (1916) (14781987942).jpg (author: Internet Archive Book Images; date: 1916 (book publication year; Young India by Lala Lajpat Rai, B.W. Huebsch, New York — Library of Congress copy, IA id youngindiainterp01lajp))</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>No restrictions</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Young_India;_an_interpretation_and_a_history_of_the_nationalist_movement_from_within_(1916)_(14781987942).jpg</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-07-20; Three sibling scans exist on Commons; disambiguated by exact scaling (1624x2396 scales to 948.9x1400, matching installed 949x1400; aspect diff 0.01%) and by the caption in extmetadata: 'Bal Ganga Dhar Tilak'. Categorized under Bal Gangadhar Tilak. It is the Tilak plate facing p. 163, not strictly the frontispiece.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>History gallery</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1917/gallery/gallery-3.png</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Bal Gangadhar Tilak in Madras 1917</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Bal Gangadhar Tilak in Madras 1917.jpg (author: Press Agency photographer; date: 1917 (credit: Imperial War Museum, object 205353560))</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Public domain</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Bal_Gangadhar_Tilak_in_Madras_1917.jpg</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-07-20; Aspect 800/464 = 1.72414 vs installed 500/290 = 1.72414 — exact match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>History gallery</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1921/gallery/gallery-1.png</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Pencil sketch: Pingley Venkayya with the Swaraj flag</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>FFOI book 'Know Your National Flag' (Lt Cdr KV Singh, Flag Foundation of India, 2013), p. 41 (scan)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>(c) Flag Foundation of India — client's own publication</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Book p. 41</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>History gallery</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1921/gallery/gallery-2.png</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CWMG, vol.20 (1921), Frontispiece, Gandhi-ji in 1921 - Code Swaraj</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:CWMG, vol.20 (1921), Frontispiece, Gandhi-ji in 1921 - Code Swaraj.jpg (author: Carl Malamud, Sam Pitroda; date: Photograph depicts Gandhi in 1921 (frontispiece of Collected Works of Mahatma Gandhi vol. 20); scan uploaded from the book Code Swaraj, file DateTime 2022-04-17)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>CC0</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:CWMG,_vol.20_(1921),_Frontispiece,_Gandhi-ji_in_1921_-_Code_Swaraj.jpg</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-07-20; Installed aspect 1048/1400 = 0.74857 vs original 1500/2003 = 0.74888, difference 0.04% (within 1%). Artist field credits the Code Swaraj authors/scanners (CC0 dedication), not the original 1921 photographer, who is unnamed on the file page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>History gallery</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1921/gallery/gallery-3.png</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Boycott of foreign clothes</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Boycott of foreign clothes.jpg (author: The Bombay Chronicle; date: 1921-07-30 (DateTimeOriginal); description: "Newspaper The Bombay Chronicle, July 30, 1921")</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Public domain</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Boycott_of_foreign_clothes.jpg</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-07-20; Exact dimension match 480x432. Register's provisional note said 31 Jul 1921; the Commons file page dates the notice to 30 Jul 1921 — update the exhibit caption accordingly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>History gallery</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1931/gallery/gallery-1.png</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Karachi Congress</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Karachi Congress.jpg (author: Unknown author; date: 1931)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Public domain</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Karachi_Congress.jpg</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-07-20; Found via Commons search 'Karachi Congress 1931'. Original 3228x2196 exactly matches the stated original size; aspect ratio differs from installed 1400x952 by 0.044%. Description: 'Karachi Congress, 1931.' Credit: scanned by Commons user Yann (Gandhi Smarak Sangrahalaya Samiti film scan).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>History gallery</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1931/gallery/gallery-2.png</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Madeleine Slade, now "Mirabehn," teaches women in Karachi about spinning and weaving</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Madeleine Slade, now "Mirabehn," teaches women in Karachi about spinning and weaving.jpg (author: Unknown author; date: 1931 (news bureau photo, per file caption))</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Public domain</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Madeleine_Slade,_now_%22Mirabehn,%22_teaches_women_in_Karachi_about_spinning_and_weaving.jpg</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-07-20; Found via Commons search 'Mirabehn Karachi'. Original 930x746 is pixel-identical to the installed 930x746 (0.000% aspect difference). Description: news bureau photo from 1931; sourced from Columbia University (F. Pritchett) page, originally from eBay Aug. 2007.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>History gallery</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1941/gallery/gallery-1.png</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1948 calendar art: Mother India with Netaji Subhash Chandra Bose</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>FFOI book 'Know Your National Flag' (Lt Cdr KV Singh, Flag Foundation of India, 2013), p. 44 (scan)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>(c) Flag Foundation of India — client's own publication</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Book p. 44</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>History gallery</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1941/gallery/gallery-2.png</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Netaji Subhas Chandra Bose Reviewing the Troops of Azad Hind Fauj - 1940's</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Netaji Subhas Chandra Bose Reviewing the Troops of Azad Hind Fauj - 1940's.jpg (author: Unknown author; date: 1940s (extmetadata DateTimeOriginal: 1940; description: "Netaji Subhas Chandra Bose Reviewing the Troops of Azad Hind Fauj - 1940's"))</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Public domain</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Netaji_Subhas_Chandra_Bose_Reviewing_the_Troops_of_Azad_Hind_Fauj_-_1940%27s.jpg</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-07-20; Provisional title 'File:Netaji Subhas Chandra Bose Reviewing the Troops of Azad Hind Fauj.jpg' does not exist on Commons; the real file adds a " - 1940's" suffix. Original size 792x561 matches installed exactly. Credit line: oldindianphotos.in (Military label).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>History gallery</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1941/gallery/gallery-3.png</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Netaji Subhas Chandra Bose and Members of the Azad Hind Fauj</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Netaji Subhas Chandra Bose and Members of the Azad Hind Fauj.jpg (author: Unknown author; date: 1940s (extmetadata DateTimeOriginal: 1940; description dates it "1940's" and names Bose with Bhonsle, Kiani, Shahnawaz Khan, Dhillon, Sahgal, Lakshmi Sahgal, Abid Hasan and others))</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Public domain</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Netaji_Subhas_Chandra_Bose_and_Members_of_the_Azad_Hind_Fauj.jpg</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-07-20; Original size 864x590 matches installed exactly. Credit line: oldindianphotos.in (Military label).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>History gallery</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1941/gallery/gallery-4.png</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Indian National Army in Rangoon, 1944</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Indian National Army in Rangoon, 1944.jpg (author: 写真週報 (Shashin Shūhō, Japanese wartime photographic weekly); date: 1944 (source issue: Shashin Shūhō No. 309, 16 February 1944 / Showa 19; INA marching in Rangoon))</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Public domain</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Indian_National_Army_in_Rangoon,_1944.jpg</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-07-20; Original size 651x465 matches installed exactly. Credit: Japan National Archives Digital Archive (digital.archives.go.jp), 写真週報 309号.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>History gallery</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1941/gallery/gallery-5.png</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>A Sikh Soldier of the Azad Hind Fauj at a function in Berlin</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:A Sikh Soldier of the Azad Hind Fauj at a function in Berlin.jpg (author: Unknown author; date: 1944 (extmetadata DateTimeOriginal: 1944; description: "A Sikh Soldier of the Azad Hind Fauj at a function in Berlin - 1944"))</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Public domain</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:A_Sikh_Soldier_of_the_Azad_Hind_Fauj_at_a_function_in_Berlin.jpg</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-07-20; Original size 596x768 matches installed exactly. Credit line: oldindianphotos.in (Military label).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>History gallery</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1947/gallery/gallery-1.png</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Pandit Nehru presenting the Tiranga to the Constituent Assembly, 22 Jul 1947</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>FFOI book 'Know Your National Flag' (Lt Cdr KV Singh, Flag Foundation of India, 2013), p. 13 (scan)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>(c) Flag Foundation of India — client's own publication</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Book p. 13</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>History gallery</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1947/gallery/gallery-2.png</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>First public flag hoisting, Princess Park, 15 Aug 1947</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>FFOI book 'Know Your National Flag' (Lt Cdr KV Singh, Flag Foundation of India, 2013), p. 17 (scan)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>(c) Flag Foundation of India — client's own publication</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Book p. 17</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>History gallery</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1947/gallery/gallery-3.png</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Chandni Chowk on 15 August 1947</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Chandni Chowk on 15 August 1947.jpg (author: photodivision.gov.in (Government of India Photo Division); date: 1947-08-15)</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Public domain</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Chandni_Chowk_on_15_August_1947.jpg</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-07-20; replaced an unattributable legacy design image</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>History gallery</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1947/gallery/gallery-4.png</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Lord Mountbatten saluting the flag, Princess Park, 15 Aug 1947</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>FFOI book 'Know Your National Flag' (Lt Cdr KV Singh, Flag Foundation of India, 2013), p. 18 (scan)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>(c) Flag Foundation of India — client's own publication</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Book p. 18</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>History gallery</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1947/gallery/gallery-5.png</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Pencil sketch: Mrs. Hansa Mehta</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>FFOI book 'Know Your National Flag' (Lt Cdr KV Singh, Flag Foundation of India, 2013), p. 15 (scan)</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>(c) Flag Foundation of India — client's own publication</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Book p. 15</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>History gallery</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1947/gallery/gallery-6.png</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Jawaharlal Nehru delivering his "tryst with destiny" speech</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Jawaharlal Nehru delivering his "tryst with destiny" speech.jpg (author: Unknown author; date: 1947-08-15)</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Public domain</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Jawaharlal_Nehru_delivering_his_"tryst_with_destiny"_speech.jpg</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>History year flag</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1906/flag/flag.png</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Official FFOI flag-evolution artwork, 1906</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>flagfoundationofindia.in (foundation's own graphic), enhanced (Magnific precision, faithful mode)</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>(c) Flag Foundation of India</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>https://flagfoundationofindia.in/uploads/flag-evolutions/01KFMS2A8A3CT9D9JEBGHW7G5P.png</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>History year flag</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1907/flag/flag.png</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Official FFOI flag-evolution artwork, 1907</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>flagfoundationofindia.in (foundation's own graphic), enhanced (Magnific precision, faithful mode)</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>(c) Flag Foundation of India</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>https://flagfoundationofindia.in/uploads/flag-evolutions/01KFMS7CGR8K6TAYT4W44B4NBD.png</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>History year flag</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1917/flag/flag.png</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Official FFOI flag-evolution artwork, 1917</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>flagfoundationofindia.in (foundation's own graphic), enhanced (Magnific precision, faithful mode)</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>(c) Flag Foundation of India</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>https://flagfoundationofindia.in/uploads/flag-evolutions/01KFMS6T7S0Y5CCZ10MZ0S0MFR.png</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>History year flag</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1921/flag/flag.png</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Official FFOI flag-evolution artwork, 1921</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>flagfoundationofindia.in (foundation's own graphic), enhanced (Magnific precision, faithful mode)</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>(c) Flag Foundation of India</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://flagfoundationofindia.in/uploads/flag-evolutions/01KFMS6A0ADGX1Q9D1ZBQFSC2J.png</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>History year flag</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1931/flag/flag.png</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Official FFOI flag-evolution artwork, 1931</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>flagfoundationofindia.in (foundation's own graphic), enhanced (Magnific precision, faithful mode)</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>(c) Flag Foundation of India</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>https://flagfoundationofindia.in/uploads/flag-evolutions/01KFMS5T8800EEQBP1VCP5DN8R.png</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>History year flag</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1947/flag/flag.png</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Official FFOI flag-evolution artwork, 1947</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>flagfoundationofindia.in (foundation's own graphic), enhanced (Magnific precision, faithful mode)</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>(c) Flag Foundation of India</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>https://flagfoundationofindia.in/uploads/flag-evolutions/01KFMS5A8CE1JRXV5SX520N2TS.png</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>History year flag</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1857/flag/flag.png</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Flag artwork for 1857 from the FFOI book</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>FFOI book 'Know Your National Flag' (Lt Cdr KV Singh, Flag Foundation of India, 2013), p. 35 (scan, page background removed, enhanced)</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>(c) Flag Foundation of India — client's own publication</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Book p. 35</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>History year flag</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1905/flag/flag.png</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Flag artwork for 1905 from the FFOI book</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>FFOI book 'Know Your National Flag' (Lt Cdr KV Singh, Flag Foundation of India, 2013), p. 36 (scan, page background removed, enhanced)</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>(c) Flag Foundation of India — client's own publication</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Book p. 36</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>History year flag</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1941/flag/flag.png</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Flag artwork for 1941 from the FFOI book</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>FFOI book 'Know Your National Flag' (Lt Cdr KV Singh, Flag Foundation of India, 2013), p. 43 (scan, page background removed, enhanced)</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>(c) Flag Foundation of India — client's own publication</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Book p. 43</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>History era background</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1906/background/bg-1.png</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Era scene for 1906 (representative art, not an archival photograph)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Client design handoff (Freepik Mystic 4K render; flags composited via Nano Banana Pro)</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Commissioned AI scene art — no third-party rights</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Design handoff bundle</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>History era background</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1907/background/bg-1.png</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Era scene for 1907 (representative art, not an archival photograph)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Client design handoff (Freepik Mystic 4K render; flags composited via Nano Banana Pro)</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Commissioned AI scene art — no third-party rights</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Design handoff bundle</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>History era background</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1917/background/bg-1.png</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Era scene for 1917 (representative art, not an archival photograph)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Client design handoff (Freepik Mystic 4K render; flags composited via Nano Banana Pro)</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Commissioned AI scene art — no third-party rights</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Design handoff bundle</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>History era background</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1921/background/bg-1.png</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Era scene for 1921 (representative art, not an archival photograph)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Client design handoff (Freepik Mystic 4K render; flags composited via Nano Banana Pro)</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Commissioned AI scene art — no third-party rights</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Design handoff bundle</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>History era background</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1931/background/bg-1.png</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Era scene for 1931 (representative art, not an archival photograph)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Client design handoff (Freepik Mystic 4K render; flags composited via Nano Banana Pro)</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Commissioned AI scene art — no third-party rights</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Design handoff bundle</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>History era background</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1947/background/bg-1.png</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Era scene for 1947 (representative art, not an archival photograph)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Client design handoff (Freepik Mystic 4K render; flags composited via Nano Banana Pro)</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Commissioned AI scene art — no third-party rights</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Design handoff bundle</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>History era background</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1857/background/bg-1.png</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Era scene for 1857 (representative art, not an archival photograph)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Generated 2026-07-19 via Magnific (Nano Banana) to match the handoff set</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Commissioned AI scene art — no third-party rights</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Sources tab, row 'Era backgrounds'</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>History era background</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1905/background/bg-1.png</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Era scene for 1905 (representative art, not an archival photograph)</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Generated 2026-07-19 via Magnific (Nano Banana) to match the handoff set</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Commissioned AI scene art — no third-party rights</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Sources tab, row 'Era backgrounds'</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>History era background</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2-history-of-tiranga/1941/background/bg-1.png</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Era scene for 1941 (representative art, not an archival photograph)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Generated 2026-07-19 via Magnific (Nano Banana) to match the handoff set</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Commissioned AI scene art — no third-party rights</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Sources tab, row 'Era backgrounds'</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0-home/background/bg.mp4 + poster.png</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Sunset monumental-flag scene (loop)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Client design handoff AI render, enhanced + normalized to 1080p</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Commissioned AI render — no third-party rights</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Design handoff bundle</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>0-home/cards/card-*.png (4 files)</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Category tile artwork</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Client Figma design exports (design file SGS26MDJpekIP2K2HKW65Z)</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Client's own design assets</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Figma file</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>0-home/logo/logo-nju.png</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Naveen Jindal Universe logo lockup</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Client Figma design export</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Client's own brand asset</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Figma file</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Monumental Flags</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>1-monumental-flags/intro/intro.mp4 + poster.png</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>India map fly-in (plays once)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Client design handoff AI render</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Commissioned AI render — no third-party rights</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Design handoff bundle</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Monumental Flags</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>1-monumental-flags/map/background/bg.mp4 + bg.png</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Terrain India map base layer</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Client design handoff AI render</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Commissioned AI render — no third-party rights</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Design handoff bundle</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Monumental Flags</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>1-monumental-flags/map/states/* (78 files)</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Per-state map artwork + tap shapes</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Client Figma design exports</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Client's own design assets</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Figma file</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Monumental Flags</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>1-monumental-flags/select-state/background/bg.png</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Glowing India render</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Client-provided render (2026-07-16)</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Client's own design asset</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Figma file</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Monumental Flags</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>1-monumental-flags/map/flag-marker/static.png</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Tricolour-on-pole map marker</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Client-provided reference graphic</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Client's own design asset</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Figma file</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Monumental Flags</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>1-monumental-flags/installations/&lt;row&gt;/1.jpg (135 sites)</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Photograph of each flag installation</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>flagfoundationofindia.in uploads — per-site URL in Excel tab 04 'Photo URL' (26 added 2026-07-19 were caption-matched + visually verified; all URLs re-checked HTTP 200)</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>(c) Flag Foundation of India — foundation's own site photos</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Excel tab 04, Photo URL column</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Ashok Chakra</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>3-ashok-chakra/background/bg.png</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Golden-sunset scene behind the 3D wheel</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Client Figma design export (AI scene render)</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Client's own design asset</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Figma file</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Ashok Chakra</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>3-ashok-chakra/flag-tab/flag-pole.png + wheel/wheel-poster.png</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Flag hero + wheel poster</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Client Figma design exports</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Client's own design assets</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Figma file</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Ashok Chakra</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>3-ashok-chakra/virtue-icons/*.svg (24)</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Virtue spoke icons</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Drawn for this project in the design's gold line style (6 from Figma, 18 created to match)</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Project-original artwork</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Figma file / repo history</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>National Symbols</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>4-national-symbols/carousel-background + detail-background</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Navy stage renders</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Client Figma design exports (AI scene renders)</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Client's own design assets</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Figma file</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>National Symbols</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/&lt;slug&gt;/turntable/ (14 symbols)</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Symbol turntable sequences and posters</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Generated for this project (client-supervised Magnific/Kling pipeline, 2026-07-18/19)</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Commissioned AI renders — no third-party rights</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>docs/SYMBOL-TURNTABLE-PROMPTS.md</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>National Symbols</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/tiger/did-you-know/1.png</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Tiger stripe close-up</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Client Figma design export</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Client's own design asset</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Figma file</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Fonts</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>_shared/fonts/Gilroy-*.ttf</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Gilroy typeface</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>User-licensed (installed from client's licensed copies)</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Licensed to client</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>License on file with client</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Fonts</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Poppins, Inter, Parisienne, Port Lligat Slab (bundled)</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Google Fonts</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>fonts.google.com</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>SIL Open Font License</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>https://fonts.google.com/attribution</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -6488,7 +9062,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>

--- a/data/content.xlsx
+++ b/data/content.xlsx
@@ -4054,7 +4054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5758,25 +5758,29 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Era scene for 1906 (representative art, not an archival photograph)</t>
+          <t>Bande Mataram Weekly Edition masthead</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Client design handoff (Freepik Mystic 4K render; flags composited via Nano Banana Pro)</t>
+          <t>Derived from 1906/gallery/gallery-2.png (crop/upscale + warm grade — REAL archival image, no AI; see that gallery row for the original source)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Commissioned AI scene art — no third-party rights</t>
+          <t>Public domain (inherited from the gallery image)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Design handoff bundle</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr"/>
+          <t>Same as the matching gallery row</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-07-20 — rebuilt from real archival photo</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5791,25 +5795,29 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Era scene for 1907 (representative art, not an archival photograph)</t>
+          <t>Delegates, Intl. Socialist Congress Stuttgart 1907</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Client design handoff (Freepik Mystic 4K render; flags composited via Nano Banana Pro)</t>
+          <t>Derived from 1907/gallery/gallery-4.png (crop/upscale + warm grade — REAL archival image, no AI; see that gallery row for the original source)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Commissioned AI scene art — no third-party rights</t>
+          <t>Public domain (inherited from the gallery image)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Design handoff bundle</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr"/>
+          <t>Same as the matching gallery row</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-07-20 — rebuilt from real archival photo</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5824,25 +5832,29 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Era scene for 1917 (representative art, not an archival photograph)</t>
+          <t>Home Rule era procession crowd</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Client design handoff (Freepik Mystic 4K render; flags composited via Nano Banana Pro)</t>
+          <t>Derived from 1917/gallery/gallery-3.png (crop/upscale + warm grade — REAL archival image, no AI; see that gallery row for the original source)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Commissioned AI scene art — no third-party rights</t>
+          <t>Public domain (inherited from the gallery image)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Design handoff bundle</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr"/>
+          <t>Same as the matching gallery row</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-07-20 — rebuilt from real archival photo</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5857,25 +5869,29 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Era scene for 1921 (representative art, not an archival photograph)</t>
+          <t>Gandhi 1921 portrait (self-blur fill composite, same photo only)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Client design handoff (Freepik Mystic 4K render; flags composited via Nano Banana Pro)</t>
+          <t>Derived from 1921/gallery/gallery-2.png (crop/upscale + warm grade — REAL archival image, no AI; see that gallery row for the original source)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Commissioned AI scene art — no third-party rights</t>
+          <t>Public domain (inherited from the gallery image)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Design handoff bundle</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr"/>
+          <t>Same as the matching gallery row</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-07-20 — rebuilt from real archival photo</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5890,25 +5906,29 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Era scene for 1931 (representative art, not an archival photograph)</t>
+          <t>Karachi Congress 1931 panorama with flag mast</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Client design handoff (Freepik Mystic 4K render; flags composited via Nano Banana Pro)</t>
+          <t>Derived from 1931/gallery/gallery-1.png (crop/upscale + warm grade — REAL archival image, no AI; see that gallery row for the original source)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Commissioned AI scene art — no third-party rights</t>
+          <t>Public domain (inherited from the gallery image)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Design handoff bundle</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr"/>
+          <t>Same as the matching gallery row</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-07-20 — rebuilt from real archival photo</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5923,25 +5943,29 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Era scene for 1947 (representative art, not an archival photograph)</t>
+          <t>Constituent Assembly, 14-15 August 1947</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Client design handoff (Freepik Mystic 4K render; flags composited via Nano Banana Pro)</t>
+          <t>Derived from 1947/gallery/gallery-6.png (crop/upscale + warm grade — REAL archival image, no AI; see that gallery row for the original source)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Commissioned AI scene art — no third-party rights</t>
+          <t>Public domain (inherited from the gallery image)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Design handoff bundle</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr"/>
+          <t>Same as the matching gallery row</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-07-20 — rebuilt from real archival photo</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5956,25 +5980,29 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Era scene for 1857 (representative art, not an archival photograph)</t>
+          <t>Battle of Delhi 1857 lithograph</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Generated 2026-07-19 via Magnific (Nano Banana) to match the handoff set</t>
+          <t>Derived from 1857/gallery/gallery-4.png (crop/upscale + warm grade — REAL archival image, no AI; see that gallery row for the original source)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Commissioned AI scene art — no third-party rights</t>
+          <t>Public domain (inherited from the gallery image)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sources tab, row 'Era backgrounds'</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr"/>
+          <t>Same as the matching gallery row</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2026-07-20 — rebuilt from real archival photo</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5989,25 +6017,29 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Era scene for 1905 (representative art, not an archival photograph)</t>
+          <t>Sister Nivedita walking with Sara Bull &amp; Josephine MacLeod</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Generated 2026-07-19 via Magnific (Nano Banana) to match the handoff set</t>
+          <t>Derived from 1905/gallery/gallery-2.png (crop/upscale + warm grade — REAL archival image, no AI; see that gallery row for the original source)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Commissioned AI scene art — no third-party rights</t>
+          <t>Public domain (inherited from the gallery image)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sources tab, row 'Era backgrounds'</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr"/>
+          <t>Same as the matching gallery row</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2026-07-20 — rebuilt from real archival photo</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6022,25 +6054,29 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Era scene for 1941 (representative art, not an archival photograph)</t>
+          <t>Subhas Chandra Bose reviewing INA troops</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Generated 2026-07-19 via Magnific (Nano Banana) to match the handoff set</t>
+          <t>Derived from 1941/gallery/gallery-2.png (crop/upscale + warm grade — REAL archival image, no AI; see that gallery row for the original source)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Commissioned AI scene art — no third-party rights</t>
+          <t>Public domain (inherited from the gallery image)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sources tab, row 'Era backgrounds'</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr"/>
+          <t>Same as the matching gallery row</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2026-07-20 — rebuilt from real archival photo</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6073,7 +6109,6 @@
           <t>Design handoff bundle</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6106,7 +6141,6 @@
           <t>Figma file</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6139,7 +6173,6 @@
           <t>Figma file</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6172,7 +6205,6 @@
           <t>Design handoff bundle</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6205,7 +6237,6 @@
           <t>Design handoff bundle</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6238,7 +6269,6 @@
           <t>Figma file</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6271,7 +6301,6 @@
           <t>Figma file</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6304,7 +6333,6 @@
           <t>Figma file</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6374,7 +6402,6 @@
           <t>Figma file</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6407,7 +6434,6 @@
           <t>Figma file</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6440,7 +6466,6 @@
           <t>Figma file / repo history</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6473,7 +6498,6 @@
           <t>Figma file</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6506,7 +6530,6 @@
           <t>docs/SYMBOL-TURNTABLE-PROMPTS.md</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6539,7 +6562,6 @@
           <t>Figma file</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6572,7 +6594,6 @@
           <t>License on file with client</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6605,7 +6626,6 @@
           <t>https://fonts.google.com/attribution</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/content.xlsx
+++ b/data/content.xlsx
@@ -5758,12 +5758,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bande Mataram Weekly Edition masthead</t>
+          <t>Bande Mataram masthead as paper-artifact card over its own blurred page</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Derived from 1906/gallery/gallery-2.png (crop/upscale + warm grade — REAL archival image, no AI; see that gallery row for the original source)</t>
+          <t>Derived from 1906/gallery/gallery-2.png (crop/composite + warm grade — REAL archival image, no AI; see that gallery row for the original source)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Home Rule era procession crowd</t>
+          <t>Bal Gangadhar Tilak 1917 portrait, self-blur fill composite</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Derived from 1917/gallery/gallery-3.png (crop/upscale + warm grade — REAL archival image, no AI; see that gallery row for the original source)</t>
+          <t>Derived from 1917/gallery/gallery-2.png (crop/composite + warm grade — REAL archival image, no AI; see that gallery row for the original source)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sister Nivedita walking with Sara Bull &amp; Josephine MacLeod</t>
+          <t>Nivedita group photo, self-blur fill composite (photo right of the year-flag slot)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Derived from 1905/gallery/gallery-2.png (crop/upscale + warm grade — REAL archival image, no AI; see that gallery row for the original source)</t>
+          <t>Derived from 1905/gallery/gallery-2.png (crop/composite + warm grade — REAL archival image, no AI; see that gallery row for the original source)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">

--- a/data/content.xlsx
+++ b/data/content.xlsx
@@ -5832,17 +5832,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bal Gangadhar Tilak 1917 portrait, self-blur fill composite</t>
+          <t>Bal Gangadhar Tilak 1917 portrait, surroundings generatively extended to widescreen (Nano Banana Pro, user-approved 2026-07-20); archival portrait unchanged</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Derived from 1917/gallery/gallery-2.png (crop/composite + warm grade — REAL archival image, no AI; see that gallery row for the original source)</t>
+          <t>Derived from 1917/gallery/gallery-2.png — archival core unchanged, margins AI-extended (Google Nano Banana Pro via Magnific); see the gallery row for the original source</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Public domain (inherited from the gallery image)</t>
+          <t>Archival core: public domain; extended margins: commissioned gen-fill, no third-party rights</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5869,17 +5869,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Gandhi 1921 portrait (self-blur fill composite, same photo only)</t>
+          <t>Gandhi 1921 portrait, surroundings generatively extended to widescreen (Nano Banana Pro, user-approved 2026-07-20); archival portrait unchanged</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Derived from 1921/gallery/gallery-2.png (crop/upscale + warm grade — REAL archival image, no AI; see that gallery row for the original source)</t>
+          <t>Derived from 1921/gallery/gallery-2.png — archival core unchanged, margins AI-extended (Google Nano Banana Pro via Magnific); see the gallery row for the original source</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Public domain (inherited from the gallery image)</t>
+          <t>Archival core: public domain; extended margins: commissioned gen-fill, no third-party rights</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -6017,17 +6017,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Nivedita group photo, self-blur fill composite (photo right of the year-flag slot)</t>
+          <t>Nivedita group photo, surroundings generatively extended to widescreen (Nano Banana Pro, user-approved 2026-07-20); archival photo unchanged</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Derived from 1905/gallery/gallery-2.png (crop/composite + warm grade — REAL archival image, no AI; see that gallery row for the original source)</t>
+          <t>Derived from 1905/gallery/gallery-2.png — archival core unchanged, margins AI-extended (Google Nano Banana Pro via Magnific); see the gallery row for the original source</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Public domain (inherited from the gallery image)</t>
+          <t>Archival core: public domain; extended margins: commissioned gen-fill, no third-party rights</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">

--- a/data/content.xlsx
+++ b/data/content.xlsx
@@ -6054,17 +6054,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Subhas Chandra Bose reviewing INA troops</t>
+          <t>Bose reviewing INA troops — scene re-rendered to widescreen by GPT 2 from the archival reference (user-approved 2026-07-20); likeness verified against the original</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Derived from 1941/gallery/gallery-2.png (crop/upscale + warm grade — REAL archival image, no AI; see that gallery row for the original source)</t>
+          <t>Derived from 1941/gallery/gallery-2.png — widescreen re-render (GPT 2 via Magnific); the true archival photo is in the 1941 gallery (see that row)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Public domain (inherited from the gallery image)</t>
+          <t>Gen-render from a public-domain reference — no third-party rights</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">

--- a/data/content.xlsx
+++ b/data/content.xlsx
@@ -5943,7 +5943,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Constituent Assembly, 14-15 August 1947</t>
+          <t>Constituent Assembly, 14-15 Aug 1947 — mirrored horizontally (user decision 2026-07-20: Nehru at the rostrum visible beside the text column)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">

--- a/data/content.xlsx
+++ b/data/content.xlsx
@@ -756,6 +756,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -1036,7 +1037,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Era backgrounds bg-1: 1906-1947 from client design handoff (Freepik Mystic 4K scene renders; flags composited via Nano Banana Pro); 1857, 1905 and 1941 generated to match via Magnific (Nano Banana, sepia era scenes). Representative scene art, not archival photographs.</t>
+          <t>Era backgrounds bg-1 (all 9 years): built from that year's own provenance-verified gallery photo (real archival images — see tab '10 · Image Credits' for per-asset detail). 1905/1917/1921: archival photo unchanged, margins AI-extended to widescreen (Nano Banana Pro, user-approved 2026-07-20). 1941: widescreen re-render from the archival reference (GPT 2, likeness verified). 1947: archival photo mirrored for composition (user decision).</t>
         </is>
       </c>
     </row>
@@ -4054,7 +4055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>

--- a/data/content.xlsx
+++ b/data/content.xlsx
@@ -756,7 +756,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -21750,7 +21749,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sister Nivedita, the Irish disciple of Swami Vivekananda, was the first to conceive a National-flag for all of India — a square red banner bordered by 108 'Jyotis', carrying the Vajra of strength and 'Vande Mataram'. The original is preserved in the Acharya Bhavan Museum, Kolkata.</t>
+          <t>Sister Nivedita, the Irish disciple of Swami Vivekananda, was the first to conceive a National-flag for all of India — a square red banner carrying the Vajra and 'Vande Mataram'.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21844,7 +21843,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>On 22 August 1907, Madam Bhikhaji Cama carried India's cause abroad, unfurling the tricolour before the International Congress at Stuttgart, Germany. That flag — evolved from the 1906 Calcutta design — is preserved in the library of 'Kesari', Pune.</t>
+          <t>On 22 August 1907, Madam Bhikhaji Cama carried India's cause abroad, unfurling the tricolour before the International Congress at Stuttgart, Germany.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">

--- a/data/content.xlsx
+++ b/data/content.xlsx
@@ -4054,7 +4054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6624,6 +6624,1967 @@
       <c r="F74" t="inlineStr">
         <is>
           <t>https://fonts.google.com/attribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/flag/did-you-know/2.png</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>PM Nehru addresses the nation from the Red Fort on 15 August 1947</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:PM_Nehru_addresses_the_nation_from_the_Red_Fort_on_15_August_1947.jpg</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Public domain</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:PM_Nehru_addresses_the_nation_from_the_Red_Fort_on_15_August_1947.jpg</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2026-07-25; Unknown author</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/flag/did-you-know/3.png</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>The waving Indian flag</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:The_waving_Indian_flag.jpg</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:The_waving_Indian_flag.jpg</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2026-07-25; Sisheer Philip</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/lion-capital-of-ashoka/did-you-know/1.png</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Sarnath capital</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Sarnath_capital.jpg</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Sarnath_capital.jpg</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2026-07-25; Chrisi1964</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/lion-capital-of-ashoka/did-you-know/2.png</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Sarnath ruins</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Sarnath_ruins.jpg</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Sarnath_ruins.jpg</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2026-07-25; Yashaswi RKG</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/jana-gana-mana/did-you-know/2.png</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Rabindranath Tagore in 1909</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Rabindranath_Tagore_in_1909.jpg</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Public domain</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Rabindranath_Tagore_in_1909.jpg</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2026-07-25; Generalstabens litografiska anstalt</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/jana-gana-mana/did-you-know/4.png</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>English translation of Jana Gana Mana in Tagore's handwriting page 1</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:English_translation_of_Jana_Gana_Mana_in_Tagore's_handwriting_page_1.jpg</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Public domain</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:English_translation_of_Jana_Gana_Mana_in_Tagore%27s_handwriting_page_1.jpg</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2026-07-25; Rabindranath Tagore</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/vande-mataram/did-you-know/1.png</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Procession at Bangalore during Quit India movement, by Indian National Congress</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Procession_at_Bangalore_during_Quit_India_movement,_by_Indian_National_Congress.jpg</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>CC BY-SA 2.5</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Procession_at_Bangalore_during_Quit_India_movement,_by_Indian_National_Congress.jpg</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2026-07-25; Indian National Congress (uploaded by Dore chakravarty)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/vande-mataram/did-you-know/2.png</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Bankimchandra Chattapadhay</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Bankimchandra_Chattapadhay.jpg</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Public domain</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Bankimchandra_Chattapadhay.jpg</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2026-07-25; Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/vande-mataram/did-you-know/3.png</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Bharat Mata by Abanindranath Tagore</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Bharat_Mata_by_Abanindranath_Tagore.jpg</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Public domain</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Bharat_Mata_by_Abanindranath_Tagore.jpg</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2026-07-25; Abanindranath Tagore</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/saka-calendar/did-you-know/2.png</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>20191218 Jantar Mantar, Jaipur 0906 8983 DxO</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:20191218_Jantar_Mantar,_Jaipur_0906_8983_DxO.jpg</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:20191218_Jantar_Mantar,_Jaipur_0906_8983_DxO.jpg</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2026-07-25; Jakub Hałun</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/tiger/did-you-know/2.png</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Royal bengal tiger Swimming</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Royal_bengal_tiger_Swimming.jpg</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Royal_bengal_tiger_Swimming.jpg</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2026-07-25; Badal Chandra Sarker</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/tiger/did-you-know/3.png</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Durga riding on a tiger in triumph with Karthikeya and Hanuman. Coloured transfer lithograph</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Durga_riding_on_a_tiger_in_triumph_with_Karthikeya_and_Hanuman._Coloured_transfer_lithograph.jpg</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Public domain</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Durga_riding_on_a_tiger_in_triumph_with_Karthikeya_and_Hanuman._Coloured_transfer_lithograph.jpg</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>2026-07-25; Amrit / Chasmanuyr Press (Wellcome Collection)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/tiger/did-you-know/4.png</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Pasupati Seal, National Museum, New Delhi</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Pasupati_Seal,_National_Museum,_New_Delhi.jpg</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>CC BY-SA 3.0</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Pasupati_Seal,_National_Museum,_New_Delhi.jpg</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>2026-07-25; Nomu420</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/tiger/did-you-know/5.png</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Bengal Tiger walking on observation line in Sundarban</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Bengal_Tiger_walking_on_observation_line_in_Sundarban.jpg</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Bengal_Tiger_walking_on_observation_line_in_Sundarban.jpg</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>2026-07-25; Soumyajit Nandy</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/peacock/did-you-know/1.png</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Detail of Indian Peacock tail feather</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Detail_of_Indian_Peacock_tail_feather.jpg</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>CC BY-SA 2.5</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Detail_of_Indian_Peacock_tail_feather.jpg</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>2026-07-25; MichaelMaggs</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/peacock/did-you-know/2.png</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Monsoon Mania - the Dancing Peacock</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Monsoon_Mania_-_the_Dancing_Peacock.jpg</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Monsoon_Mania_-_the_Dancing_Peacock.jpg</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>2026-07-25; Sanjay Ojha</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/peacock/did-you-know/3.png</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Murugan by Raja Ravi Varma</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Murugan_by_Raja_Ravi_Varma.jpg</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Public domain</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Murugan_by_Raja_Ravi_Varma.jpg</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>2026-07-25; Raja Ravi Varma</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/lotus/did-you-know/1.png</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Nelumbo Nucifera Lotus Flower (223664533)</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Nelumbo_Nucifera_Lotus_Flower_(223664533).jpeg</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>CC BY 3.0</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Nelumbo_Nucifera_Lotus_Flower_(223664533).jpeg</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>2026-07-25; Tasha Carl</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/lotus/did-you-know/2.png</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Lotus Nelumbo nucifera Water Drops 2654px</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Lotus_Nelumbo_nucifera_Water_Drops_2654px.jpg</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>CC BY-SA 3.0</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Lotus_Nelumbo_nucifera_Water_Drops_2654px.jpg</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>2026-07-25; Derek Ramsey (Ram-Man)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/lotus/did-you-know/4.png</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Raja Ravi Varma, Goddess Lakshmi, 1896</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Raja_Ravi_Varma,_Goddess_Lakshmi,_1896.jpg</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Public domain</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Raja_Ravi_Varma,_Goddess_Lakshmi,_1896.jpg</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>2026-07-25; Raja Ravi Varma</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/indian-banyan/did-you-know/1.png</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Big Banyan Tree at Bangalore</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Big_Banyan_Tree_at_Bangalore.jpg</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>CC BY-SA 2.5</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Big_Banyan_Tree_at_Bangalore.jpg</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>2026-07-25; Kiran Gopi</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/indian-banyan/did-you-know/2.png</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Thimmamma Marrimanu Anantapur dt Andhra JEG9111</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Thimmamma_Marrimanu_Anantapur_dt_Andhra_JEG9111.JPG</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Thimmamma_Marrimanu_Anantapur_dt_Andhra_JEG9111.JPG</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>2026-07-25; P. Jeganathan</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/indian-banyan/did-you-know/3.png</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Idols under banyan tree - panoramio</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Idols_under_banyan_tree_-_panoramio.jpg</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>CC BY 3.0</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Idols_under_banyan_tree_-_panoramio.jpg</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>2026-07-25; Suresh Babunair</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/mango/did-you-know/1.png</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Mango orchard in Lucknow</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Mango_orchard_in_Lucknow.jpg</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Mango_orchard_in_Lucknow.jpg</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>2026-07-25; Zainab37</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/mango/did-you-know/2.png</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Mangoes hanging on the tree. 01</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Mangoes_hanging_on_the_tree._01.jpg</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>CC BY 4.0</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Mangoes_hanging_on_the_tree._01.jpg</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>2026-07-25; Denis kasozi</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/mango/did-you-know/4.png</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>India, Kashmir - Shawl with boteh - 1952.190 - Cleveland Museum of Art</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:India,_Kashmir_-_Shawl_with_boteh_-_1952.190_-_Cleveland_Museum_of_Art.tif</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>CC0</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:India,_Kashmir_-_Shawl_with_boteh_-_1952.190_-_Cleveland_Museum_of_Art.tif</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>2026-07-25; Cleveland Museum of Art</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/ganga/did-you-know/1.png</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Aerial View Ganga River Banks, Varanasi India 2012</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Aerial_View_Ganga_River_Banks,_Varanasi_India_2012.jpg</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>CC BY 2.0</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Aerial_View_Ganga_River_Banks,_Varanasi_India_2012.jpg</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>2026-07-25; La Fessée</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/ganga/did-you-know/2.png</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Ganga Aarti at Varanasi</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Ganga_Aarti_at_Varanasi.jpg</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Ganga_Aarti_at_Varanasi.jpg</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>2026-07-25; Abhishek Dixit Ji</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/ganga/did-you-know/3.png</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Gaumukh Glacier</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Gaumukh_Glacier.jpg</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Gaumukh_Glacier.jpg</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>2026-07-25; ShekharRawat07</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/ganga/did-you-know/4.png</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Morning bath at Varanasi ghats</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Morning_bath_at_Varanasi_ghats.JPG</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>CC BY 3.0</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Morning_bath_at_Varanasi_ghats.JPG</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>2026-07-25; Ilya Mauter</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/ganges-river-dolphin/did-you-know/1.png</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Ganges River Dolphin</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Ganges_River_Dolphin.jpg</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Ganges_River_Dolphin.jpg</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>2026-07-25; Kukil Gogoi</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/ganges-river-dolphin/did-you-know/3.png</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>FMIB 34107 Platanista gangetica, (Lebeck) Wagler The Susu</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:FMIB_34107_Platanista_gangetica,_(Lebeck)_Wagler_The_Susu.jpeg</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Public domain</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:FMIB_34107_Platanista_gangetica,_(Lebeck)_Wagler_The_Susu.jpeg</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>2026-07-25; Frederick W. True (after Eschricht)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/indian-rupee/did-you-know/2.png</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Sher shah's rupee</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Sher_shah's_rupee.jpg</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>CC BY-SA 3.0</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Sher_shah%27s_rupee.jpg</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>2026-07-25; Drnsreedhar (English Wikipedia)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/indian-elephant/did-you-know/1.png</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Stone sculpture of Ganesha, British Museum 01</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Stone_sculpture_of_Ganesha,_British_Museum_01.jpg</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>CC0</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Stone_sculpture_of_Ganesha,_British_Museum_01.jpg</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>2026-07-25; 14GTR</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/indian-elephant/did-you-know/2.png</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Aarattu procession elephant carrying deity, Kerala , India</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Aarattu_procession_elephant_carrying_deity,_Kerala_,_India.jpg</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Aarattu_procession_elephant_carrying_deity,_Kerala_,_India.jpg</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>2026-07-25; Aexthetic</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/indian-elephant/did-you-know/3.png</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>The Elephant Herd at Kabini</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:The_Elephant_Herd_at_Kabini.jpg</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:The_Elephant_Herd_at_Kabini.jpg</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>2026-07-25; Shravya S Narayan</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/indian-elephant/did-you-know/4.png</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Elephant scape</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Elephant_scape.jpg</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>CC0</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Elephant_scape.jpg</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>2026-07-25; UdayKiran28</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/flag/did-you-know/4.png</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Ashoka Chakra</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons — File:Ashoka_Chakra.svg</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Public domain</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Ashoka_Chakra.svg</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>2026-07-25; Government of India</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/flag/did-you-know/1.png</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Child holding the Tiranga aloft</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>AI-generated — Magnific (Google Nano Banana 2)</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AI-generated; no third-party rights</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/lion-capital-of-ashoka/did-you-know/3.png</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Polished Mauryan sandstone macro</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>AI-generated — Magnific (Google Nano Banana 2)</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AI-generated; no third-party rights</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/jana-gana-mana/did-you-know/1.png</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Crowd at a flag ceremony</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>AI-generated — Magnific (Google Nano Banana 2)</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AI-generated; no third-party rights</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/jana-gana-mana/did-you-know/3.png</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>India rivers and mountain ranges montage</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>AI-generated — Magnific (Google Nano Banana 2)</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AI-generated; no third-party rights</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/saka-calendar/did-you-know/1.png</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Sunrise over the horizon</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>AI-generated — Magnific (Google Nano Banana 2)</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AI-generated; no third-party rights</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/tiger/did-you-know/1.png</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Tiger flank stripe macro</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>AI-generated — Magnific (Google Nano Banana 2)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AI-generated; no third-party rights</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/peacock/did-you-know/4.png</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Peacock feather on a Krishna-blue ground</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>AI-generated — Magnific (Google Nano Banana 2)</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AI-generated; no third-party rights</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/lotus/did-you-know/3.png</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Lotus rising from a muddy pond</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>AI-generated — Magnific (Google Nano Banana 2)</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AI-generated; no third-party rights</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/indian-banyan/did-you-know/4.png</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Villagers gathered under a banyan</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>AI-generated — Magnific (Google Nano Banana 2)</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AI-generated; no third-party rights</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/mango/did-you-know/3.png</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Assorted mango varieties, flat-lay</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>AI-generated — Magnific (Google Nano Banana 2)</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AI-generated; no third-party rights</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/ganges-river-dolphin/did-you-know/2.png</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Wide Ganga riverscape, hint of a fin</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>AI-generated — Magnific (Google Nano Banana 2)</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AI-generated; no third-party rights</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/ganges-river-dolphin/did-you-know/4.png</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Researchers surveying the river at dawn</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>AI-generated — Magnific (Google Nano Banana 2)</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AI-generated; no third-party rights</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/indian-rupee/did-you-know/1.png</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Indian Rupee sign — gold hero render</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>AI-generated — Magnific (GPT-2)</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AI-generated; no third-party rights</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/indian-rupee/did-you-know/3.png</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Indian Rupee sign — construction diagram</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>AI-generated — Magnific (GPT-2)</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AI-generated; no third-party rights</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>National Symbols — Did You Know</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>4-national-symbols/symbols/indian-rupee/did-you-know/4.png</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>World currency symbols, Rupee highlighted</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>AI-generated — Magnific (GPT-2)</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AI-generated; no third-party rights</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>
@@ -13554,7 +15515,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -13868,7 +15828,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>

--- a/data/content.xlsx
+++ b/data/content.xlsx
@@ -8961,7 +8961,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Scientific name: Panthera Tigris</t>
+          <t>Scientific name: Panthera tigris</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Species: Ficus Benghalensis</t>
+          <t>Species: Ficus benghalensis</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -14185,7 +14185,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Army Cantonement</t>
+          <t>Army Cantonment</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15076,7 +15076,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Meerut Cantonement</t>
+          <t>Meerut Cantonment</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15406,7 +15406,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>yamuna nagar</t>
+          <t>Yamuna Nagar</t>
         </is>
       </c>
       <c r="F135" t="n">
